--- a/database.xlsx
+++ b/database.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phase-Figs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0662FC-05C5-4180-8F4A-99352BBA503E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF98A35D-F22E-42EF-B9F0-77403034F7C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5304" yWindow="0" windowWidth="14856" windowHeight="11976" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20430" yWindow="8370" windowWidth="14850" windowHeight="9450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="41">
   <si>
     <t>Ag</t>
   </si>
@@ -140,7 +140,15 @@
     <t>Match4</t>
   </si>
   <si>
-    <t>AgCC</t>
+    <t>Ag</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sn</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bi</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -491,12 +499,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D63435DF-52DE-4DA4-ACBB-D3A0B8F017C0}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14.5" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="19" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -596,6 +604,9 @@
       <c r="E5" t="s">
         <v>5</v>
       </c>
+      <c r="F5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
@@ -1058,35 +1069,52 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B30" s="1">
-        <v>125.62</v>
+        <v>118.7</v>
       </c>
       <c r="C30" s="1">
-        <v>1473</v>
+        <v>231.9</v>
       </c>
       <c r="D30" s="1">
-        <v>5</v>
+        <v>7.03</v>
       </c>
       <c r="E30" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B31" s="1">
+        <v>125.62</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1473</v>
+      </c>
+      <c r="D31" s="1">
+        <v>5</v>
+      </c>
+      <c r="E31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B32" s="1">
         <v>65.38</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C32" s="1">
         <v>419.5</v>
       </c>
-      <c r="D31" s="1">
+      <c r="D32" s="1">
         <v>7.3</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E32" t="s">
         <v>12</v>
       </c>
     </row>
